--- a/data/trans_dic/P2A_ner_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,03</t>
+          <t>3,25; 5,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 6,32</t>
+          <t>3,21; 6,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,06; 9,88</t>
+          <t>5,84; 9,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,75</t>
+          <t>3,26; 7,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,19</t>
+          <t>5,53; 8,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,23</t>
+          <t>6,3; 9,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,07; 21,31</t>
+          <t>16,06; 21,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 8,99</t>
+          <t>6,28; 9,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,89; 6,75</t>
+          <t>4,81; 6,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,31; 7,32</t>
+          <t>5,33; 7,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,24; 15,53</t>
+          <t>12,29; 15,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,38; 7,59</t>
+          <t>5,48; 7,62</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,69</t>
+          <t>1,35; 2,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,05</t>
+          <t>1,58; 2,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,73</t>
+          <t>3,01; 4,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,02</t>
+          <t>2,08; 4,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,65</t>
+          <t>2,84; 4,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,3</t>
+          <t>2,42; 4,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,85; 10,45</t>
+          <t>7,69; 10,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 37,36</t>
+          <t>3,82; 34,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,34</t>
+          <t>2,19; 3,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,29</t>
+          <t>2,25; 3,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,56; 7,16</t>
+          <t>5,51; 7,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 23,62</t>
+          <t>3,28; 22,78</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,09</t>
+          <t>1,26; 3,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,02</t>
+          <t>2,02; 5,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,96</t>
+          <t>1,74; 4,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,45</t>
+          <t>1,57; 4,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,98</t>
+          <t>0,65; 3,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,25</t>
+          <t>1,71; 5,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,54</t>
+          <t>2,91; 6,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,32</t>
+          <t>1,78; 4,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,93</t>
+          <t>1,23; 2,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,13</t>
+          <t>2,31; 4,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,17</t>
+          <t>2,65; 5,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,69</t>
+          <t>1,97; 3,74</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,4</t>
+          <t>2,25; 3,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,74</t>
+          <t>2,5; 3,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 5,25</t>
+          <t>3,93; 5,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,03</t>
+          <t>2,49; 3,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,36</t>
+          <t>3,93; 5,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,69</t>
+          <t>4,23; 5,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,96; 12,1</t>
+          <t>9,95; 12,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 27,06</t>
+          <t>4,41; 26,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,19</t>
+          <t>3,27; 4,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,51; 4,49</t>
+          <t>3,56; 4,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,23; 8,54</t>
+          <t>7,19; 8,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,7; 16,69</t>
+          <t>3,72; 16,95</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34218; 62214</t>
+          <t>33521; 60210</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32156; 61553</t>
+          <t>31248; 60127</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45682; 74493</t>
+          <t>44079; 74558</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16865; 34736</t>
+          <t>16767; 36167</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>71254; 107740</t>
+          <t>72758; 110250</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82985; 123534</t>
+          <t>84232; 120861</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>159845; 211913</t>
+          <t>159728; 213138</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46695; 67934</t>
+          <t>47417; 70296</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>114725; 158451</t>
+          <t>112922; 159213</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>122684; 169232</t>
+          <t>123225; 170548</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>214114; 271661</t>
+          <t>214867; 277446</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>68359; 96490</t>
+          <t>69611; 96770</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22987; 45548</t>
+          <t>22835; 45509</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31043; 59840</t>
+          <t>30975; 57432</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61495; 98243</t>
+          <t>62524; 97092</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46999; 92004</t>
+          <t>47571; 94103</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44089; 73763</t>
+          <t>45057; 76368</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44527; 75531</t>
+          <t>42536; 74352</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>156035; 207786</t>
+          <t>152934; 206190</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>87244; 836127</t>
+          <t>85530; 768522</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>73251; 109460</t>
+          <t>72017; 109541</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81238; 122339</t>
+          <t>83618; 123242</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>226116; 291085</t>
+          <t>224129; 288036</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>149724; 1069555</t>
+          <t>148606; 1031290</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8070; 22544</t>
+          <t>6964; 19973</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10754; 28962</t>
+          <t>9742; 27482</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8950; 27135</t>
+          <t>9518; 27058</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10269; 28768</t>
+          <t>10131; 28863</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3037; 14179</t>
+          <t>3077; 14476</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7290; 24081</t>
+          <t>7837; 23965</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14963; 35891</t>
+          <t>15987; 37210</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11667; 28511</t>
+          <t>11726; 26576</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12521; 30068</t>
+          <t>12618; 29899</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22154; 48184</t>
+          <t>21740; 46830</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28277; 56657</t>
+          <t>29079; 55984</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24909; 48286</t>
+          <t>25688; 48900</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>72645; 111320</t>
+          <t>73626; 110999</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>83723; 128065</t>
+          <t>85410; 128325</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>131129; 177404</t>
+          <t>132583; 179043</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84800; 139246</t>
+          <t>85883; 136606</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>129417; 181201</t>
+          <t>132695; 182661</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>150708; 202115</t>
+          <t>150335; 203274</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>351646; 427379</t>
+          <t>351364; 429350</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>161898; 988686</t>
+          <t>161224; 975108</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>216538; 278899</t>
+          <t>217358; 277457</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>244741; 313242</t>
+          <t>248123; 315135</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>499749; 589795</t>
+          <t>496942; 591848</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>262695; 1186078</t>
+          <t>264233; 1204134</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_ner_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 5,84</t>
+          <t>3,34; 5,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,17</t>
+          <t>3,24; 6,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,84; 9,88</t>
+          <t>6,09; 9,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 7,02</t>
+          <t>3,44; 7,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,53; 8,38</t>
+          <t>5,59; 8,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 9,03</t>
+          <t>6,28; 9,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,06; 21,43</t>
+          <t>16,11; 21,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,28; 9,3</t>
+          <t>6,35; 9,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 6,78</t>
+          <t>4,85; 6,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,33; 7,38</t>
+          <t>5,42; 7,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,29; 15,86</t>
+          <t>12,23; 15,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 7,62</t>
+          <t>5,61; 7,77</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,69</t>
+          <t>1,36; 2,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,92</t>
+          <t>1,59; 2,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 4,68</t>
+          <t>3,0; 4,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,11</t>
+          <t>2,54; 4,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,81</t>
+          <t>2,78; 4,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,23</t>
+          <t>2,51; 4,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,69; 10,37</t>
+          <t>7,73; 10,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 34,34</t>
+          <t>3,67; 5,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,34</t>
+          <t>2,2; 3,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,31</t>
+          <t>2,26; 3,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,51; 7,09</t>
+          <t>5,62; 7,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 22,78</t>
+          <t>3,28; 4,5</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,62</t>
+          <t>1,37; 3,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,71</t>
+          <t>2,08; 5,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,95</t>
+          <t>1,8; 5,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,46</t>
+          <t>1,5; 4,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,04</t>
+          <t>0,64; 3,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,23</t>
+          <t>1,55; 5,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 6,78</t>
+          <t>2,81; 6,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,02</t>
+          <t>1,84; 4,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,91</t>
+          <t>1,19; 2,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,98</t>
+          <t>2,35; 5,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,11</t>
+          <t>2,7; 5,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,74</t>
+          <t>1,98; 3,73</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,39</t>
+          <t>2,26; 3,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 3,75</t>
+          <t>2,44; 3,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,3</t>
+          <t>3,8; 5,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 3,96</t>
+          <t>2,87; 4,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,41</t>
+          <t>3,85; 5,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 5,72</t>
+          <t>4,23; 5,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,95; 12,16</t>
+          <t>9,91; 12,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 26,69</t>
+          <t>4,21; 5,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 4,17</t>
+          <t>3,24; 4,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 4,52</t>
+          <t>3,53; 4,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 8,57</t>
+          <t>7,17; 8,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 16,95</t>
+          <t>3,73; 4,62</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24847</t>
+          <t>28660</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>57245</t>
+          <t>62931</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82092</t>
+          <t>91590</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>33521; 60210</t>
+          <t>34431; 60220</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31248; 60127</t>
+          <t>31575; 61180</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44079; 74558</t>
+          <t>45957; 74723</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16767; 36167</t>
+          <t>19876; 41228</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>72758; 110250</t>
+          <t>73494; 109522</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84232; 120861</t>
+          <t>84075; 123607</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>159728; 213138</t>
+          <t>160284; 210834</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47417; 70296</t>
+          <t>52217; 75876</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>112922; 159213</t>
+          <t>113710; 158237</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>123225; 170548</t>
+          <t>125337; 170393</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>214867; 277446</t>
+          <t>213869; 274357</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>69611; 96770</t>
+          <t>78517; 108760</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69751</t>
+          <t>73762</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>287907</t>
+          <t>95534</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>357658</t>
+          <t>169295</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22835; 45509</t>
+          <t>23009; 44725</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30975; 57432</t>
+          <t>31259; 57783</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62524; 97092</t>
+          <t>62334; 97118</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47571; 94103</t>
+          <t>56638; 94932</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45057; 76368</t>
+          <t>44083; 73436</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42536; 74352</t>
+          <t>44179; 74315</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>152934; 206190</t>
+          <t>153775; 207385</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85530; 768522</t>
+          <t>79675; 114598</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>72017; 109541</t>
+          <t>72300; 111662</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>83618; 123242</t>
+          <t>84137; 122325</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>224129; 288036</t>
+          <t>228406; 291911</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>148606; 1031290</t>
+          <t>144467; 198303</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17246</t>
+          <t>18297</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17975</t>
+          <t>20595</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35220</t>
+          <t>38892</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6964; 19973</t>
+          <t>7563; 21278</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9742; 27482</t>
+          <t>10000; 27118</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9518; 27058</t>
+          <t>9861; 28154</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10131; 28863</t>
+          <t>10701; 28916</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3077; 14476</t>
+          <t>3048; 14348</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7837; 23965</t>
+          <t>7100; 23313</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15987; 37210</t>
+          <t>15416; 36020</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11726; 26576</t>
+          <t>13500; 30096</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12618; 29899</t>
+          <t>12226; 30066</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21740; 46830</t>
+          <t>22131; 47030</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29079; 55984</t>
+          <t>29570; 55565</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25688; 48900</t>
+          <t>28643; 54019</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111843</t>
+          <t>120719</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>363127</t>
+          <t>179059</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>474971</t>
+          <t>299778</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>73626; 110999</t>
+          <t>74179; 109749</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85410; 128325</t>
+          <t>83585; 126994</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>132583; 179043</t>
+          <t>128203; 179584</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85883; 136606</t>
+          <t>100953; 147433</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>132695; 182661</t>
+          <t>129995; 181669</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>150335; 203274</t>
+          <t>150299; 202908</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>351364; 429350</t>
+          <t>349970; 428311</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>161224; 975108</t>
+          <t>156784; 204166</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>217358; 277457</t>
+          <t>215957; 278037</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>248123; 315135</t>
+          <t>246398; 314170</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>496942; 591848</t>
+          <t>495159; 587691</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>264233; 1204134</t>
+          <t>270649; 335163</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_ner_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
